--- a/data/credit_bond_2026-10-15.xlsx
+++ b/data/credit_bond_2026-10-15.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-15" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-16" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>10-15 17:00</t>
+          <t>10-15 19:00</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -719,8 +719,12 @@
           <t>1.20 ~ 2.00</t>
         </is>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>61.06</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>1.93</t>
@@ -738,7 +742,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>2.0993</t>
+          <t>2.0889</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -921,7 +925,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>10-15 18:00</t>
+          <t>10-15 19:00</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -962,7 +966,7 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>2.0166</t>
+          <t>1.9915</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">

--- a/data/credit_bond_2026-10-15.xlsx
+++ b/data/credit_bond_2026-10-15.xlsx
@@ -947,8 +947,12 @@
           <t>1.80 ~ 2.80</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>62.0</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>2.10</t>

--- a/data/credit_bond_2026-10-15.xlsx
+++ b/data/credit_bond_2026-10-15.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-16" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-19" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,9 @@
       <c r="E4" s="4" t="n">
         <v>4.5</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="4" t="n">
+        <v>4.5</v>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>1.80 ~ 2.80</t>
@@ -985,7 +987,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C- 20.58</t>
+          <t>C- 20.22</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1008,7 +1010,9 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="U4" s="3"/>
+      <c r="U4" s="4" t="n">
+        <v>5.6</v>
+      </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>

--- a/data/credit_bond_2026-10-15.xlsx
+++ b/data/credit_bond_2026-10-15.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-19" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-20" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,9 @@
       <c r="E3" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>1.20 ~ 2.00</t>
@@ -757,7 +759,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>D+ 10.00</t>
+          <t>D 5.00</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -780,7 +782,9 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="U3" s="3"/>
+      <c r="U3" s="4" t="n">
+        <v>2.82</v>
+      </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3" t="inlineStr">
         <is>
@@ -987,7 +991,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C- 20.22</t>
+          <t>C- 22.13</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1087,7 +1091,7 @@
       <c r="AK4" s="3"/>
       <c r="AL4" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AM4" s="3" t="inlineStr">

--- a/data/credit_bond_2026-10-15.xlsx
+++ b/data/credit_bond_2026-10-15.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-20" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-21" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       <c r="AK3" s="3"/>
       <c r="AL3" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AM3" s="3" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C- 22.13</t>
+          <t>C- 19.19</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">

--- a/data/credit_bond_2026-10-15.xlsx
+++ b/data/credit_bond_2026-10-15.xlsx
@@ -692,7 +692,7 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26株产K1</t>
+          <t>26鸿飞03</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -702,49 +702,49 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>284148.SH</t>
+          <t>284202.SH</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>5.0</v>
+        <v>4.5</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>5.0</v>
+        <v>4.5</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.00</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>61.06</v>
+        <v>62.0</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>26株产01</t>
+          <t>26鸿飞02</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>4.88Y</t>
+          <t>4.78Y</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>2.0889</t>
+          <t>1.9915</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -754,12 +754,12 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>株洲高科产业投资集团有限公司</t>
+          <t>江油鸿飞投资(集团)有限公司</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>D 5.00</t>
+          <t>C- 19.19</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -779,47 +779,51 @@
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="U3" s="4" t="n">
-        <v>2.82</v>
+        <v>5.6</v>
       </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>1.90%~2.00%</t>
+          <t>2.21%~2.31%</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z3" s="3"/>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA3" s="3" t="inlineStr">
         <is>
-          <t>湖南省-株洲市</t>
+          <t>四川省-绵阳市</t>
         </is>
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将4.07亿元通过基金出资或置换前12个月基金出资方式用于科技创新领域,剩余部分用于偿还有息负债。</t>
+          <t>本次公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券24鸿飞01的本金。[24鸿飞01]</t>
         </is>
       </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
-          <t>财信证券股份有限公司,中银国际证券股份有限公司,国开证券股份有限公司,华金证券股份有限公司</t>
+          <t>长城证券股份有限公司</t>
         </is>
       </c>
       <c r="AD3" s="3" t="inlineStr">
         <is>
-          <t>湖南财鑫融资担保有限公司</t>
+          <t>成都中小企业融资担保有限责任公司</t>
         </is>
       </c>
       <c r="AE3" s="3" t="inlineStr">
@@ -839,7 +843,7 @@
       </c>
       <c r="AH3" s="3" t="inlineStr">
         <is>
-          <t>株洲高科产业投资集团有限公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
+          <t>江油鸿飞投资(集团)有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI3" s="3" t="inlineStr">
@@ -849,13 +853,13 @@
       </c>
       <c r="AJ3" s="3" t="inlineStr">
         <is>
-          <t>2029-10-19</t>
+          <t>2031-10-16</t>
         </is>
       </c>
       <c r="AK3" s="3"/>
       <c r="AL3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AM3" s="3" t="inlineStr">
@@ -865,33 +869,37 @@
       </c>
       <c r="AN3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP3" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
       <c r="AQ3" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT3" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU3" s="3" t="inlineStr">
@@ -924,7 +932,7 @@
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26鸿飞03</t>
+          <t>26株产K1</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -934,49 +942,49 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>284202.SH</t>
+          <t>284148.SH</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>4.5</v>
+        <v>5.0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>4.5</v>
+        <v>5.0</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.20 ~ 2.00</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>62.0</v>
+        <v>61.06</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>26鸿飞02</t>
+          <t>26株产01</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>4.78Y</t>
+          <t>4.88Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1.9915</t>
+          <t>2.0889</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -986,12 +994,12 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>江油鸿飞投资(集团)有限公司</t>
+          <t>株洲高科产业投资集团有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C- 19.19</t>
+          <t>D 5.00</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1011,51 +1019,47 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="U4" s="4" t="n">
-        <v>5.6</v>
+        <v>2.82</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>2.21%~2.31%</t>
+          <t>1.90%~2.00%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>四川省-绵阳市</t>
+          <t>湖南省-株洲市</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>本次公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券24鸿飞01的本金。[24鸿飞01]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将4.07亿元通过基金出资或置换前12个月基金出资方式用于科技创新领域,剩余部分用于偿还有息负债。</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>长城证券股份有限公司</t>
+          <t>财信证券股份有限公司,中银国际证券股份有限公司,国开证券股份有限公司,华金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>成都中小企业融资担保有限责任公司</t>
+          <t>湖南财鑫融资担保有限公司</t>
         </is>
       </c>
       <c r="AE4" s="3" t="inlineStr">
@@ -1075,7 +1079,7 @@
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>江油鸿飞投资(集团)有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>株洲高科产业投资集团有限公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
@@ -1085,13 +1089,13 @@
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2031-10-16</t>
+          <t>2029-10-19</t>
         </is>
       </c>
       <c r="AK4" s="3"/>
       <c r="AL4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AM4" s="3" t="inlineStr">
@@ -1101,37 +1105,33 @@
       </c>
       <c r="AN4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP4" s="3"/>
       <c r="AQ4" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU4" s="3" t="inlineStr">
